--- a/Configs/GameConfig/Datas/Skills.xlsx
+++ b/Configs/GameConfig/Datas/Skills.xlsx
@@ -795,19 +795,19 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
+  <cols xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
     <col min="1" max="1" width="9" hidden="0" customWidth="1"/>
-    <col min="2" max="2" width="22" hidden="0" customWidth="1"/>
-    <col min="3" max="3" width="22" hidden="0" customWidth="1"/>
-    <col min="4" max="4" width="22" hidden="0" customWidth="1"/>
+    <col min="2" max="2" width="23" hidden="0" customWidth="1"/>
+    <col min="3" max="3" width="32" hidden="0" customWidth="1"/>
+    <col min="4" max="4" width="14" hidden="0" customWidth="1"/>
     <col min="5" max="5" width="22" hidden="0" customWidth="1"/>
-    <col min="6" max="6" width="22" hidden="0" customWidth="1"/>
-    <col min="7" max="7" width="22" hidden="0" customWidth="1"/>
-    <col min="8" max="8" width="22" hidden="0" customWidth="1"/>
-    <col min="9" max="9" width="32" hidden="0" customWidth="1"/>
+    <col min="6" max="6" width="11" hidden="0" customWidth="1"/>
+    <col min="7" max="7" width="18" hidden="0" customWidth="1"/>
+    <col min="8" max="8" width="24" hidden="0" customWidth="1"/>
+    <col min="9" max="9" width="38" hidden="0" customWidth="1"/>
   </cols>
-  <sheetData>
-    <row r="1" ht="23" customHeight="1">
+  <sheetData xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+    <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="str">
         <v>##var</v>
       </c>
@@ -818,25 +818,19 @@
         <v>LegacyId</v>
       </c>
       <c r="D1" s="1" t="str">
-        <v>Level</v>
+        <v>NameCn</v>
       </c>
       <c r="E1" s="1" t="str">
-        <v>NameCn</v>
+        <v>Effect</v>
       </c>
       <c r="F1" s="1" t="str">
-        <v>LearnSoul</v>
-      </c>
-      <c r="G1" s="1" t="str">
-        <v>Effect</v>
-      </c>
-      <c r="H1" s="1" t="str">
-        <v>Value</v>
-      </c>
-      <c r="I1" s="1" t="str">
-        <v>Description</v>
-      </c>
-    </row>
-    <row r="2" ht="23" customHeight="1">
+        <v>*Levels</v>
+      </c>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1"/>
+      <c r="I1" s="1"/>
+    </row>
+    <row r="2" ht="20" customHeight="1">
       <c r="A2" s="1" t="str">
         <v>##var</v>
       </c>
@@ -844,758 +838,462 @@
       <c r="C2" s="1"/>
       <c r="D2" s="1"/>
       <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-      <c r="H2" s="1"/>
-      <c r="I2" s="1"/>
-    </row>
-    <row r="3" ht="23" customHeight="1">
+      <c r="F2" s="1" t="str">
+        <v>Level</v>
+      </c>
+      <c r="G2" s="1" t="str">
+        <v>LearnSoul</v>
+      </c>
+      <c r="H2" s="1" t="str">
+        <v>Value</v>
+      </c>
+      <c r="I2" s="1" t="str">
+        <v>Description</v>
+      </c>
+    </row>
+    <row r="3" ht="45" customHeight="1">
       <c r="A3" s="1" t="str">
-        <v>##type</v>
+        <v>##</v>
       </c>
       <c r="B3" s="1" t="str">
-        <v>Skills.PassiveId</v>
+        <v>被动技能编号</v>
       </c>
       <c r="C3" s="1" t="str">
-        <v>string</v>
+        <v>造一被动数组下标</v>
       </c>
       <c r="D3" s="1" t="str">
-        <v>int</v>
+        <v>官方技能名</v>
       </c>
       <c r="E3" s="1" t="str">
-        <v>string</v>
+        <v>效果类型</v>
       </c>
       <c r="F3" s="1" t="str">
-        <v>int</v>
+        <v>等级：1..5</v>
       </c>
       <c r="G3" s="1" t="str">
-        <v>Skills.PassiveEffect</v>
+        <v>购买本级灵魂费用</v>
       </c>
       <c r="H3" s="1" t="str">
-        <v>float</v>
+        <v>本级总加成；概率用0..1</v>
       </c>
       <c r="I3" s="1" t="str">
-        <v>string</v>
-      </c>
-    </row>
-    <row r="4" ht="23" customHeight="1">
-      <c r="A4" s="1" t="str">
-        <v>##group</v>
-      </c>
-      <c r="B4" s="1"/>
-      <c r="C4" s="1"/>
-      <c r="D4" s="1"/>
-      <c r="E4" s="1"/>
-      <c r="F4" s="1"/>
-      <c r="G4" s="1"/>
-      <c r="H4" s="1"/>
-      <c r="I4" s="1"/>
-    </row>
-    <row r="5" ht="64" customHeight="1">
-      <c r="A5" s="1" t="str">
-        <v>##</v>
-      </c>
-      <c r="B5" s="1" t="str">
-        <v>被动技能；两名角色共用规则</v>
-      </c>
-      <c r="C5" s="1" t="str">
-        <v>造一被动数组下标</v>
-      </c>
-      <c r="D5" s="1" t="str">
-        <v>购买后的等级：1..5</v>
-      </c>
-      <c r="E5" s="1" t="str">
-        <v>官方技能名</v>
-      </c>
-      <c r="F5" s="1" t="str">
-        <v>购买本级的灵魂费用</v>
-      </c>
-      <c r="G5" s="1" t="str">
-        <v>官方效果；狂暴是概率而非现有Crit等级</v>
-      </c>
-      <c r="H5" s="1" t="str">
-        <v>本级总加成；暴击率用0..1，其余为属性点/每秒值</v>
-      </c>
-      <c r="I5" s="1" t="str">
         <v>官方本级效果说明</v>
       </c>
     </row>
-    <row r="6" ht="23" customHeight="1">
-      <c r="A6" s="2"/>
-      <c r="B6" s="2" t="str">
+    <row r="4" ht="20" customHeight="1">
+      <c r="B4" s="2" t="str">
         <v>Vitality</v>
       </c>
-      <c r="C6" s="2" t="str">
+      <c r="C4" s="2" t="str">
         <v>official.ispassiveskill[0]</v>
       </c>
-      <c r="D6" s="2" t="n">
+      <c r="D4" s="2" t="str">
+        <v>热血</v>
+      </c>
+      <c r="E4" s="2" t="str">
+        <v>MaxHealth</v>
+      </c>
+      <c r="F4" s="2">
         <v>1</v>
       </c>
-      <c r="E6" s="2" t="str">
-        <v>热血</v>
-      </c>
-      <c r="F6" s="2" t="n">
+      <c r="G4" s="2">
         <v>5000</v>
       </c>
-      <c r="G6" s="2" t="str">
-        <v>MaxHealth</v>
-      </c>
-      <c r="H6" s="2" t="n">
+      <c r="H4" s="2">
         <v>200</v>
       </c>
+      <c r="I4" s="2" t="str">
+        <v>生命上限增加 200</v>
+      </c>
+    </row>
+    <row r="5" ht="20" customHeight="1">
+      <c r="F5" s="2">
+        <v>2</v>
+      </c>
+      <c r="G5" s="2">
+        <v>10000</v>
+      </c>
+      <c r="H5" s="2">
+        <v>300</v>
+      </c>
+      <c r="I5" s="2" t="str">
+        <v>生命上限增加 300</v>
+      </c>
+    </row>
+    <row r="6" ht="20" customHeight="1">
+      <c r="F6" s="2">
+        <v>3</v>
+      </c>
+      <c r="G6" s="2">
+        <v>15000</v>
+      </c>
+      <c r="H6" s="2">
+        <v>400</v>
+      </c>
       <c r="I6" s="2" t="str">
-        <v>生命上限增加 200</v>
-      </c>
-    </row>
-    <row r="7" ht="23" customHeight="1">
-      <c r="A7" s="2"/>
-      <c r="B7" s="2" t="str">
-        <v>Vitality</v>
-      </c>
-      <c r="C7" s="2" t="str">
-        <v>official.ispassiveskill[0]</v>
-      </c>
-      <c r="D7" s="2" t="n">
+        <v>生命上限增加 400</v>
+      </c>
+    </row>
+    <row r="7" ht="20" customHeight="1">
+      <c r="F7" s="2">
+        <v>4</v>
+      </c>
+      <c r="G7" s="2">
+        <v>20000</v>
+      </c>
+      <c r="H7" s="2">
+        <v>500</v>
+      </c>
+      <c r="I7" s="2" t="str">
+        <v>生命上限增加 500</v>
+      </c>
+    </row>
+    <row r="8" ht="20" customHeight="1">
+      <c r="F8" s="2">
+        <v>5</v>
+      </c>
+      <c r="G8" s="2">
+        <v>25000</v>
+      </c>
+      <c r="H8" s="2">
+        <v>600</v>
+      </c>
+      <c r="I8" s="2" t="str">
+        <v>生命上限增加 600</v>
+      </c>
+    </row>
+    <row r="9" ht="20" customHeight="1">
+      <c r="B9" s="2" t="str">
+        <v>ManaSpring</v>
+      </c>
+      <c r="C9" s="2" t="str">
+        <v>official.ispassiveskill[1]</v>
+      </c>
+      <c r="D9" s="2" t="str">
+        <v>魔泉</v>
+      </c>
+      <c r="E9" s="2" t="str">
+        <v>MaxMana</v>
+      </c>
+      <c r="F9" s="2">
+        <v>1</v>
+      </c>
+      <c r="G9" s="2">
+        <v>5000</v>
+      </c>
+      <c r="H9" s="2">
+        <v>200</v>
+      </c>
+      <c r="I9" s="2" t="str">
+        <v>魔法上限增加 200</v>
+      </c>
+    </row>
+    <row r="10" ht="20" customHeight="1">
+      <c r="F10" s="2">
         <v>2</v>
       </c>
-      <c r="E7" s="2" t="str">
-        <v>热血</v>
-      </c>
-      <c r="F7" s="2" t="n">
+      <c r="G10" s="2">
         <v>10000</v>
       </c>
-      <c r="G7" s="2" t="str">
-        <v>MaxHealth</v>
-      </c>
-      <c r="H7" s="2" t="n">
+      <c r="H10" s="2">
         <v>300</v>
       </c>
-      <c r="I7" s="2" t="str">
-        <v>生命上限增加 300</v>
-      </c>
-    </row>
-    <row r="8" ht="23" customHeight="1">
-      <c r="A8" s="2"/>
-      <c r="B8" s="2" t="str">
-        <v>Vitality</v>
-      </c>
-      <c r="C8" s="2" t="str">
-        <v>official.ispassiveskill[0]</v>
-      </c>
-      <c r="D8" s="2" t="n">
+      <c r="I10" s="2" t="str">
+        <v>魔法上限增加 300</v>
+      </c>
+    </row>
+    <row r="11" ht="20" customHeight="1">
+      <c r="F11" s="2">
         <v>3</v>
       </c>
-      <c r="E8" s="2" t="str">
-        <v>热血</v>
-      </c>
-      <c r="F8" s="2" t="n">
+      <c r="G11" s="2">
         <v>15000</v>
       </c>
-      <c r="G8" s="2" t="str">
-        <v>MaxHealth</v>
-      </c>
-      <c r="H8" s="2" t="n">
+      <c r="H11" s="2">
         <v>400</v>
       </c>
-      <c r="I8" s="2" t="str">
-        <v>生命上限增加 400</v>
-      </c>
-    </row>
-    <row r="9" ht="23" customHeight="1">
-      <c r="A9" s="2"/>
-      <c r="B9" s="2" t="str">
-        <v>Vitality</v>
-      </c>
-      <c r="C9" s="2" t="str">
-        <v>official.ispassiveskill[0]</v>
-      </c>
-      <c r="D9" s="2" t="n">
+      <c r="I11" s="2" t="str">
+        <v>魔法上限增加 400</v>
+      </c>
+    </row>
+    <row r="12" ht="20" customHeight="1">
+      <c r="F12" s="2">
         <v>4</v>
       </c>
-      <c r="E9" s="2" t="str">
-        <v>热血</v>
-      </c>
-      <c r="F9" s="2" t="n">
+      <c r="G12" s="2">
         <v>20000</v>
       </c>
-      <c r="G9" s="2" t="str">
-        <v>MaxHealth</v>
-      </c>
-      <c r="H9" s="2" t="n">
+      <c r="H12" s="2">
         <v>500</v>
       </c>
-      <c r="I9" s="2" t="str">
-        <v>生命上限增加 500</v>
-      </c>
-    </row>
-    <row r="10" ht="23" customHeight="1">
-      <c r="A10" s="2"/>
-      <c r="B10" s="2" t="str">
-        <v>Vitality</v>
-      </c>
-      <c r="C10" s="2" t="str">
-        <v>official.ispassiveskill[0]</v>
-      </c>
-      <c r="D10" s="2" t="n">
+      <c r="I12" s="2" t="str">
+        <v>魔法上限增加 500</v>
+      </c>
+    </row>
+    <row r="13" ht="20" customHeight="1">
+      <c r="F13" s="2">
         <v>5</v>
       </c>
-      <c r="E10" s="2" t="str">
-        <v>热血</v>
-      </c>
-      <c r="F10" s="2" t="n">
+      <c r="G13" s="2">
         <v>25000</v>
       </c>
-      <c r="G10" s="2" t="str">
-        <v>MaxHealth</v>
-      </c>
-      <c r="H10" s="2" t="n">
+      <c r="H13" s="2">
         <v>600</v>
       </c>
-      <c r="I10" s="2" t="str">
-        <v>生命上限增加 600</v>
-      </c>
-    </row>
-    <row r="11" ht="23" customHeight="1">
-      <c r="A11" s="2"/>
-      <c r="B11" s="2" t="str">
-        <v>ManaSpring</v>
-      </c>
-      <c r="C11" s="2" t="str">
-        <v>official.ispassiveskill[1]</v>
-      </c>
-      <c r="D11" s="2" t="n">
+      <c r="I13" s="2" t="str">
+        <v>魔法上限增加 600</v>
+      </c>
+    </row>
+    <row r="14" ht="20" customHeight="1">
+      <c r="B14" s="2" t="str">
+        <v>Frenzy</v>
+      </c>
+      <c r="C14" s="2" t="str">
+        <v>official.ispassiveskill[2]</v>
+      </c>
+      <c r="D14" s="2" t="str">
+        <v>狂暴</v>
+      </c>
+      <c r="E14" s="2" t="str">
+        <v>CriticalChance</v>
+      </c>
+      <c r="F14" s="2">
         <v>1</v>
       </c>
-      <c r="E11" s="2" t="str">
-        <v>魔泉</v>
-      </c>
-      <c r="F11" s="2" t="n">
+      <c r="G14" s="2">
         <v>5000</v>
       </c>
-      <c r="G11" s="2" t="str">
-        <v>MaxMana</v>
-      </c>
-      <c r="H11" s="2" t="n">
-        <v>200</v>
-      </c>
-      <c r="I11" s="2" t="str">
-        <v>魔法上限增加 200</v>
-      </c>
-    </row>
-    <row r="12" ht="23" customHeight="1">
-      <c r="A12" s="2"/>
-      <c r="B12" s="2" t="str">
-        <v>ManaSpring</v>
-      </c>
-      <c r="C12" s="2" t="str">
-        <v>official.ispassiveskill[1]</v>
-      </c>
-      <c r="D12" s="2" t="n">
+      <c r="H14" s="2">
+        <v>0.02</v>
+      </c>
+      <c r="I14" s="2" t="str">
+        <v>暴击率增加 2 %</v>
+      </c>
+    </row>
+    <row r="15" ht="20" customHeight="1">
+      <c r="F15" s="2">
         <v>2</v>
       </c>
-      <c r="E12" s="2" t="str">
-        <v>魔泉</v>
-      </c>
-      <c r="F12" s="2" t="n">
+      <c r="G15" s="2">
         <v>10000</v>
       </c>
-      <c r="G12" s="2" t="str">
-        <v>MaxMana</v>
-      </c>
-      <c r="H12" s="2" t="n">
-        <v>300</v>
-      </c>
-      <c r="I12" s="2" t="str">
-        <v>魔法上限增加 300</v>
-      </c>
-    </row>
-    <row r="13" ht="23" customHeight="1">
-      <c r="A13" s="2"/>
-      <c r="B13" s="2" t="str">
-        <v>ManaSpring</v>
-      </c>
-      <c r="C13" s="2" t="str">
-        <v>official.ispassiveskill[1]</v>
-      </c>
-      <c r="D13" s="2" t="n">
+      <c r="H15" s="2">
+        <v>0.03</v>
+      </c>
+      <c r="I15" s="2" t="str">
+        <v>暴击率增加 3 %</v>
+      </c>
+    </row>
+    <row r="16" ht="20" customHeight="1">
+      <c r="F16" s="2">
         <v>3</v>
       </c>
-      <c r="E13" s="2" t="str">
-        <v>魔泉</v>
-      </c>
-      <c r="F13" s="2" t="n">
+      <c r="G16" s="2">
         <v>15000</v>
       </c>
-      <c r="G13" s="2" t="str">
-        <v>MaxMana</v>
-      </c>
-      <c r="H13" s="2" t="n">
-        <v>400</v>
-      </c>
-      <c r="I13" s="2" t="str">
-        <v>魔法上限增加 400</v>
-      </c>
-    </row>
-    <row r="14" ht="23" customHeight="1">
-      <c r="A14" s="2"/>
-      <c r="B14" s="2" t="str">
-        <v>ManaSpring</v>
-      </c>
-      <c r="C14" s="2" t="str">
-        <v>official.ispassiveskill[1]</v>
-      </c>
-      <c r="D14" s="2" t="n">
+      <c r="H16" s="2">
+        <v>0.04</v>
+      </c>
+      <c r="I16" s="2" t="str">
+        <v>暴击率增加 4 %</v>
+      </c>
+    </row>
+    <row r="17" ht="20" customHeight="1">
+      <c r="F17" s="2">
         <v>4</v>
       </c>
-      <c r="E14" s="2" t="str">
-        <v>魔泉</v>
-      </c>
-      <c r="F14" s="2" t="n">
+      <c r="G17" s="2">
         <v>20000</v>
       </c>
-      <c r="G14" s="2" t="str">
-        <v>MaxMana</v>
-      </c>
-      <c r="H14" s="2" t="n">
-        <v>500</v>
-      </c>
-      <c r="I14" s="2" t="str">
-        <v>魔法上限增加 500</v>
-      </c>
-    </row>
-    <row r="15" ht="23" customHeight="1">
-      <c r="A15" s="2"/>
-      <c r="B15" s="2" t="str">
-        <v>ManaSpring</v>
-      </c>
-      <c r="C15" s="2" t="str">
-        <v>official.ispassiveskill[1]</v>
-      </c>
-      <c r="D15" s="2" t="n">
+      <c r="H17" s="2">
+        <v>0.05</v>
+      </c>
+      <c r="I17" s="2" t="str">
+        <v>暴击率增加 5 %</v>
+      </c>
+    </row>
+    <row r="18" ht="20" customHeight="1">
+      <c r="F18" s="2">
         <v>5</v>
       </c>
-      <c r="E15" s="2" t="str">
-        <v>魔泉</v>
-      </c>
-      <c r="F15" s="2" t="n">
+      <c r="G18" s="2">
         <v>25000</v>
       </c>
-      <c r="G15" s="2" t="str">
-        <v>MaxMana</v>
-      </c>
-      <c r="H15" s="2" t="n">
-        <v>600</v>
-      </c>
-      <c r="I15" s="2" t="str">
-        <v>魔法上限增加 600</v>
-      </c>
-    </row>
-    <row r="16" ht="23" customHeight="1">
-      <c r="A16" s="2"/>
-      <c r="B16" s="2" t="str">
-        <v>Frenzy</v>
-      </c>
-      <c r="C16" s="2" t="str">
-        <v>official.ispassiveskill[2]</v>
-      </c>
-      <c r="D16" s="2" t="n">
+      <c r="H18" s="2">
+        <v>0.06</v>
+      </c>
+      <c r="I18" s="2" t="str">
+        <v>暴击率增加 6 %</v>
+      </c>
+    </row>
+    <row r="19" ht="20" customHeight="1">
+      <c r="B19" s="2" t="str">
+        <v>EternalLight</v>
+      </c>
+      <c r="C19" s="2" t="str">
+        <v>official.ispassiveskill[3]</v>
+      </c>
+      <c r="D19" s="2" t="str">
+        <v>光之永恒</v>
+      </c>
+      <c r="E19" s="2" t="str">
+        <v>HealthRegen</v>
+      </c>
+      <c r="F19" s="2">
         <v>1</v>
       </c>
-      <c r="E16" s="2" t="str">
-        <v>狂暴</v>
-      </c>
-      <c r="F16" s="2" t="n">
+      <c r="G19" s="2">
         <v>5000</v>
       </c>
-      <c r="G16" s="2" t="str">
-        <v>CriticalChance</v>
-      </c>
-      <c r="H16" s="2" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="I16" s="2" t="str">
-        <v>暴击率增加 2 %</v>
-      </c>
-    </row>
-    <row r="17" ht="23" customHeight="1">
-      <c r="A17" s="2"/>
-      <c r="B17" s="2" t="str">
-        <v>Frenzy</v>
-      </c>
-      <c r="C17" s="2" t="str">
-        <v>official.ispassiveskill[2]</v>
-      </c>
-      <c r="D17" s="2" t="n">
+      <c r="H19" s="2">
         <v>2</v>
       </c>
-      <c r="E17" s="2" t="str">
-        <v>狂暴</v>
-      </c>
-      <c r="F17" s="2" t="n">
+      <c r="I19" s="2" t="str">
+        <v>每秒回血增加 2</v>
+      </c>
+    </row>
+    <row r="20" ht="20" customHeight="1">
+      <c r="F20" s="2">
+        <v>2</v>
+      </c>
+      <c r="G20" s="2">
         <v>10000</v>
       </c>
-      <c r="G17" s="2" t="str">
-        <v>CriticalChance</v>
-      </c>
-      <c r="H17" s="2" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="I17" s="2" t="str">
-        <v>暴击率增加 3 %</v>
-      </c>
-    </row>
-    <row r="18" ht="23" customHeight="1">
-      <c r="A18" s="2"/>
-      <c r="B18" s="2" t="str">
-        <v>Frenzy</v>
-      </c>
-      <c r="C18" s="2" t="str">
-        <v>official.ispassiveskill[2]</v>
-      </c>
-      <c r="D18" s="2" t="n">
+      <c r="H20" s="2">
         <v>3</v>
       </c>
-      <c r="E18" s="2" t="str">
-        <v>狂暴</v>
-      </c>
-      <c r="F18" s="2" t="n">
+      <c r="I20" s="2" t="str">
+        <v>每秒回血增加 3</v>
+      </c>
+    </row>
+    <row r="21" ht="20" customHeight="1">
+      <c r="F21" s="2">
+        <v>3</v>
+      </c>
+      <c r="G21" s="2">
         <v>15000</v>
       </c>
-      <c r="G18" s="2" t="str">
-        <v>CriticalChance</v>
-      </c>
-      <c r="H18" s="2" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="I18" s="2" t="str">
-        <v>暴击率增加 4 %</v>
-      </c>
-    </row>
-    <row r="19" ht="23" customHeight="1">
-      <c r="A19" s="2"/>
-      <c r="B19" s="2" t="str">
-        <v>Frenzy</v>
-      </c>
-      <c r="C19" s="2" t="str">
-        <v>official.ispassiveskill[2]</v>
-      </c>
-      <c r="D19" s="2" t="n">
+      <c r="H21" s="2">
         <v>4</v>
       </c>
-      <c r="E19" s="2" t="str">
-        <v>狂暴</v>
-      </c>
-      <c r="F19" s="2" t="n">
+      <c r="I21" s="2" t="str">
+        <v>每秒回血增加 4</v>
+      </c>
+    </row>
+    <row r="22" ht="20" customHeight="1">
+      <c r="F22" s="2">
+        <v>4</v>
+      </c>
+      <c r="G22" s="2">
         <v>20000</v>
       </c>
-      <c r="G19" s="2" t="str">
-        <v>CriticalChance</v>
-      </c>
-      <c r="H19" s="2" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="I19" s="2" t="str">
-        <v>暴击率增加 5 %</v>
-      </c>
-    </row>
-    <row r="20" ht="23" customHeight="1">
-      <c r="A20" s="2"/>
-      <c r="B20" s="2" t="str">
-        <v>Frenzy</v>
-      </c>
-      <c r="C20" s="2" t="str">
-        <v>official.ispassiveskill[2]</v>
-      </c>
-      <c r="D20" s="2" t="n">
+      <c r="H22" s="2">
         <v>5</v>
       </c>
-      <c r="E20" s="2" t="str">
-        <v>狂暴</v>
-      </c>
-      <c r="F20" s="2" t="n">
+      <c r="I22" s="2" t="str">
+        <v>每秒回血增加 5</v>
+      </c>
+    </row>
+    <row r="23" ht="20" customHeight="1">
+      <c r="F23" s="2">
+        <v>5</v>
+      </c>
+      <c r="G23" s="2">
         <v>25000</v>
       </c>
-      <c r="G20" s="2" t="str">
-        <v>CriticalChance</v>
-      </c>
-      <c r="H20" s="2" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="I20" s="2" t="str">
-        <v>暴击率增加 6 %</v>
-      </c>
-    </row>
-    <row r="21" ht="23" customHeight="1">
-      <c r="A21" s="2"/>
-      <c r="B21" s="2" t="str">
-        <v>EternalLight</v>
-      </c>
-      <c r="C21" s="2" t="str">
-        <v>official.ispassiveskill[3]</v>
-      </c>
-      <c r="D21" s="2" t="n">
+      <c r="H23" s="2">
+        <v>6</v>
+      </c>
+      <c r="I23" s="2" t="str">
+        <v>每秒回血增加 6</v>
+      </c>
+    </row>
+    <row r="24" ht="20" customHeight="1">
+      <c r="B24" s="2" t="str">
+        <v>MoonBrilliance</v>
+      </c>
+      <c r="C24" s="2" t="str">
+        <v>official.ispassiveskill[4]</v>
+      </c>
+      <c r="D24" s="2" t="str">
+        <v>月之辉煌</v>
+      </c>
+      <c r="E24" s="2" t="str">
+        <v>ManaRegen</v>
+      </c>
+      <c r="F24" s="2">
         <v>1</v>
       </c>
-      <c r="E21" s="2" t="str">
-        <v>光之永恒</v>
-      </c>
-      <c r="F21" s="2" t="n">
+      <c r="G24" s="2">
         <v>5000</v>
       </c>
-      <c r="G21" s="2" t="str">
-        <v>HealthRegen</v>
-      </c>
-      <c r="H21" s="2" t="n">
+      <c r="H24" s="2">
         <v>2</v>
       </c>
-      <c r="I21" s="2" t="str">
-        <v>每秒回血增加 2</v>
-      </c>
-    </row>
-    <row r="22" ht="23" customHeight="1">
-      <c r="A22" s="2"/>
-      <c r="B22" s="2" t="str">
-        <v>EternalLight</v>
-      </c>
-      <c r="C22" s="2" t="str">
-        <v>official.ispassiveskill[3]</v>
-      </c>
-      <c r="D22" s="2" t="n">
+      <c r="I24" s="2" t="str">
+        <v>每秒回魔增加 2</v>
+      </c>
+    </row>
+    <row r="25" ht="20" customHeight="1">
+      <c r="F25" s="2">
         <v>2</v>
       </c>
-      <c r="E22" s="2" t="str">
-        <v>光之永恒</v>
-      </c>
-      <c r="F22" s="2" t="n">
+      <c r="G25" s="2">
         <v>10000</v>
       </c>
-      <c r="G22" s="2" t="str">
-        <v>HealthRegen</v>
-      </c>
-      <c r="H22" s="2" t="n">
+      <c r="H25" s="2">
         <v>3</v>
       </c>
-      <c r="I22" s="2" t="str">
-        <v>每秒回血增加 3</v>
-      </c>
-    </row>
-    <row r="23" ht="23" customHeight="1">
-      <c r="A23" s="2"/>
-      <c r="B23" s="2" t="str">
-        <v>EternalLight</v>
-      </c>
-      <c r="C23" s="2" t="str">
-        <v>official.ispassiveskill[3]</v>
-      </c>
-      <c r="D23" s="2" t="n">
+      <c r="I25" s="2" t="str">
+        <v>每秒回魔增加 3</v>
+      </c>
+    </row>
+    <row r="26" ht="20" customHeight="1">
+      <c r="F26" s="2">
         <v>3</v>
       </c>
-      <c r="E23" s="2" t="str">
-        <v>光之永恒</v>
-      </c>
-      <c r="F23" s="2" t="n">
+      <c r="G26" s="2">
         <v>15000</v>
       </c>
-      <c r="G23" s="2" t="str">
-        <v>HealthRegen</v>
-      </c>
-      <c r="H23" s="2" t="n">
+      <c r="H26" s="2">
         <v>4</v>
       </c>
-      <c r="I23" s="2" t="str">
-        <v>每秒回血增加 4</v>
-      </c>
-    </row>
-    <row r="24" ht="23" customHeight="1">
-      <c r="A24" s="2"/>
-      <c r="B24" s="2" t="str">
-        <v>EternalLight</v>
-      </c>
-      <c r="C24" s="2" t="str">
-        <v>official.ispassiveskill[3]</v>
-      </c>
-      <c r="D24" s="2" t="n">
+      <c r="I26" s="2" t="str">
+        <v>每秒回魔增加 4</v>
+      </c>
+    </row>
+    <row r="27" ht="20" customHeight="1">
+      <c r="F27" s="2">
         <v>4</v>
       </c>
-      <c r="E24" s="2" t="str">
-        <v>光之永恒</v>
-      </c>
-      <c r="F24" s="2" t="n">
+      <c r="G27" s="2">
         <v>20000</v>
       </c>
-      <c r="G24" s="2" t="str">
-        <v>HealthRegen</v>
-      </c>
-      <c r="H24" s="2" t="n">
+      <c r="H27" s="2">
         <v>5</v>
       </c>
-      <c r="I24" s="2" t="str">
-        <v>每秒回血增加 5</v>
-      </c>
-    </row>
-    <row r="25" ht="23" customHeight="1">
-      <c r="A25" s="2"/>
-      <c r="B25" s="2" t="str">
-        <v>EternalLight</v>
-      </c>
-      <c r="C25" s="2" t="str">
-        <v>official.ispassiveskill[3]</v>
-      </c>
-      <c r="D25" s="2" t="n">
+      <c r="I27" s="2" t="str">
+        <v>每秒回魔增加 5</v>
+      </c>
+    </row>
+    <row r="28" ht="20" customHeight="1">
+      <c r="F28" s="2">
         <v>5</v>
       </c>
-      <c r="E25" s="2" t="str">
-        <v>光之永恒</v>
-      </c>
-      <c r="F25" s="2" t="n">
+      <c r="G28" s="2">
         <v>25000</v>
       </c>
-      <c r="G25" s="2" t="str">
-        <v>HealthRegen</v>
-      </c>
-      <c r="H25" s="2" t="n">
+      <c r="H28" s="2">
         <v>6</v>
       </c>
-      <c r="I25" s="2" t="str">
-        <v>每秒回血增加 6</v>
-      </c>
-    </row>
-    <row r="26" ht="23" customHeight="1">
-      <c r="A26" s="2"/>
-      <c r="B26" s="2" t="str">
-        <v>MoonBrilliance</v>
-      </c>
-      <c r="C26" s="2" t="str">
-        <v>official.ispassiveskill[4]</v>
-      </c>
-      <c r="D26" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="E26" s="2" t="str">
-        <v>月之辉煌</v>
-      </c>
-      <c r="F26" s="2" t="n">
-        <v>5000</v>
-      </c>
-      <c r="G26" s="2" t="str">
-        <v>ManaRegen</v>
-      </c>
-      <c r="H26" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="I26" s="2" t="str">
-        <v>每秒回魔增加 2</v>
-      </c>
-    </row>
-    <row r="27" ht="23" customHeight="1">
-      <c r="A27" s="2"/>
-      <c r="B27" s="2" t="str">
-        <v>MoonBrilliance</v>
-      </c>
-      <c r="C27" s="2" t="str">
-        <v>official.ispassiveskill[4]</v>
-      </c>
-      <c r="D27" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="E27" s="2" t="str">
-        <v>月之辉煌</v>
-      </c>
-      <c r="F27" s="2" t="n">
-        <v>10000</v>
-      </c>
-      <c r="G27" s="2" t="str">
-        <v>ManaRegen</v>
-      </c>
-      <c r="H27" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="I27" s="2" t="str">
-        <v>每秒回魔增加 3</v>
-      </c>
-    </row>
-    <row r="28" ht="23" customHeight="1">
-      <c r="A28" s="2"/>
-      <c r="B28" s="2" t="str">
-        <v>MoonBrilliance</v>
-      </c>
-      <c r="C28" s="2" t="str">
-        <v>official.ispassiveskill[4]</v>
-      </c>
-      <c r="D28" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="E28" s="2" t="str">
-        <v>月之辉煌</v>
-      </c>
-      <c r="F28" s="2" t="n">
-        <v>15000</v>
-      </c>
-      <c r="G28" s="2" t="str">
-        <v>ManaRegen</v>
-      </c>
-      <c r="H28" s="2" t="n">
-        <v>4</v>
-      </c>
       <c r="I28" s="2" t="str">
-        <v>每秒回魔增加 4</v>
-      </c>
-    </row>
-    <row r="29" ht="23" customHeight="1">
-      <c r="A29" s="2"/>
-      <c r="B29" s="2" t="str">
-        <v>MoonBrilliance</v>
-      </c>
-      <c r="C29" s="2" t="str">
-        <v>official.ispassiveskill[4]</v>
-      </c>
-      <c r="D29" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="E29" s="2" t="str">
-        <v>月之辉煌</v>
-      </c>
-      <c r="F29" s="2" t="n">
-        <v>20000</v>
-      </c>
-      <c r="G29" s="2" t="str">
-        <v>ManaRegen</v>
-      </c>
-      <c r="H29" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="I29" s="2" t="str">
-        <v>每秒回魔增加 5</v>
-      </c>
-    </row>
-    <row r="30" ht="23" customHeight="1">
-      <c r="A30" s="2"/>
-      <c r="B30" s="2" t="str">
-        <v>MoonBrilliance</v>
-      </c>
-      <c r="C30" s="2" t="str">
-        <v>official.ispassiveskill[4]</v>
-      </c>
-      <c r="D30" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="E30" s="2" t="str">
-        <v>月之辉煌</v>
-      </c>
-      <c r="F30" s="2" t="n">
-        <v>25000</v>
-      </c>
-      <c r="G30" s="2" t="str">
-        <v>ManaRegen</v>
-      </c>
-      <c r="H30" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="I30" s="2" t="str">
         <v>每秒回魔增加 6</v>
       </c>
     </row>
   </sheetData>
+  <mergeCells xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1">
+    <mergeCell ref="F1:I1"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>